--- a/data/staging/source/1.2electric.xlsx
+++ b/data/staging/source/1.2electric.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maejo365-my.sharepoint.com/personal/researchmju_mju_ac_th/Documents/RAE-Document-Center/07-GreenOffice/resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{B123507F-AE86-4D30-ACF2-EB8587520D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A6FCE12-86EF-45FB-BA01-12FB7DA932F4}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{B123507F-AE86-4D30-ACF2-EB8587520D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C2FB205-55A4-48B6-9080-053FA4954495}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{150D84F5-2079-49F3-B53F-3CC6B2C0B5A9}"/>
   </bookViews>
   <sheets>
     <sheet name="2569" sheetId="2" r:id="rId1"/>
-    <sheet name="2568" sheetId="3" r:id="rId2"/>
+    <sheet name="2568" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
@@ -767,9 +767,6 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -781,6 +778,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -800,17 +800,17 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="เปอร์เซ็นต์ 2" xfId="4" xr:uid="{DD84383B-683C-4EA5-9481-B635A5E1AE9B}"/>
     <cellStyle name="จุลภาค 2" xfId="3" xr:uid="{52C6AE2E-B120-42D9-8D0C-E1572A374689}"/>
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
     <cellStyle name="ปกติ 2" xfId="1" xr:uid="{9F93A6A8-1D45-4598-A94B-0CF8EC19902F}"/>
     <cellStyle name="ปกติ 3" xfId="2" xr:uid="{108431DD-7004-474E-9580-79A989290292}"/>
   </cellStyles>
@@ -830,7 +830,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1120,7 +1120,7 @@
                   <c:v>43975.200000000186</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>-8038867.2000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1135,7 +1135,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>22049.533333333366</c:v>
+                  <c:v>-647856.06666666665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1351,7 +1351,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1730,7 +1730,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2009,28 +2009,28 @@
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>304.45106382979122</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>322.34042553191489</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>351.08297872340228</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>460.59361702127461</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>425.668085106381</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>482.87659574468483</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>467.82127659574667</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>-85519.863829787239</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -2045,7 +2045,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>-6892.0858156028371</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2260,7 +2260,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2430,7 +2430,7 @@
                   <c:v>403036.79999999981</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>264594.40000000037</c:v>
+                  <c:v>-7774272.7999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2610,7 +2610,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2748,7 +2748,7 @@
                   <c:v>386.5594288368174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-82705.029787234045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2927,7 +2927,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3352,7 +3352,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3699,7 +3699,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4262,7 +4262,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4641,7 +4641,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="th-TH"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10823,41 +10823,41 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:16" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:16" s="6" customFormat="1" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44" t="s">
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="44"/>
+      <c r="K3" s="43"/>
       <c r="M3" s="7" t="s">
         <v>6</v>
       </c>
@@ -10866,7 +10866,7 @@
       <c r="P3" s="8"/>
     </row>
     <row r="4" spans="1:16" s="6" customFormat="1" ht="54" customHeight="1" thickBot="1">
-      <c r="A4" s="43"/>
+      <c r="A4" s="42"/>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -10928,7 +10928,9 @@
         <f>C5/B5</f>
         <v>24.72964539007145</v>
       </c>
-      <c r="F5" s="13"/>
+      <c r="F5" s="13">
+        <v>94</v>
+      </c>
       <c r="G5" s="13">
         <f>P5</f>
         <v>28618.400000000373</v>
@@ -10937,17 +10939,17 @@
         <f>G5*5.42</f>
         <v>155111.72800000201</v>
       </c>
-      <c r="I5" s="12" t="e">
+      <c r="I5" s="12">
         <f>G5/F5</f>
-        <v>#DIV/0!</v>
+        <v>304.45106382979122</v>
       </c>
       <c r="J5" s="14">
         <f>(G5-C5)/C5</f>
         <v>0.64149038682144277</v>
       </c>
-      <c r="K5" s="15" t="e">
+      <c r="K5" s="15">
         <f>(I5-E5)/E5</f>
-        <v>#DIV/0!</v>
+        <v>11.311177901160823</v>
       </c>
       <c r="M5" s="16" t="s">
         <v>19</v>
@@ -10983,7 +10985,9 @@
         <f t="shared" ref="E6:E16" si="0">C6/B6</f>
         <v>19.724516129031809</v>
       </c>
-      <c r="F6" s="13"/>
+      <c r="F6" s="13">
+        <v>94</v>
+      </c>
       <c r="G6" s="13">
         <f t="shared" ref="G6:G16" si="1">P6</f>
         <v>30300</v>
@@ -10992,17 +10996,17 @@
         <f t="shared" ref="H6:H16" si="2">G6*5.42</f>
         <v>164226</v>
       </c>
-      <c r="I6" s="12" t="e">
+      <c r="I6" s="12">
         <f t="shared" ref="I6:I16" si="3">G6/F6</f>
-        <v>#DIV/0!</v>
+        <v>322.34042553191489</v>
       </c>
       <c r="J6" s="14">
         <f t="shared" ref="J6:J16" si="4">(G6-C6)/C6</f>
         <v>0.2388381905603266</v>
       </c>
-      <c r="K6" s="15" t="e">
+      <c r="K6" s="15">
         <f t="shared" ref="K6:K18" si="5">(I6-E6)/E6</f>
-        <v>#DIV/0!</v>
+        <v>15.342120811646859</v>
       </c>
       <c r="M6" s="16" t="s">
         <v>21</v>
@@ -11038,7 +11042,9 @@
         <f t="shared" si="0"/>
         <v>26.306478873239566</v>
       </c>
-      <c r="F7" s="13"/>
+      <c r="F7" s="13">
+        <v>94</v>
+      </c>
       <c r="G7" s="13">
         <f t="shared" si="1"/>
         <v>33001.799999999814</v>
@@ -11047,17 +11053,17 @@
         <f t="shared" si="2"/>
         <v>178869.75599999898</v>
       </c>
-      <c r="I7" s="12" t="e">
+      <c r="I7" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>351.08297872340228</v>
       </c>
       <c r="J7" s="14">
         <f t="shared" si="4"/>
         <v>-0.11654066903671646</v>
       </c>
-      <c r="K7" s="15" t="e">
+      <c r="K7" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>12.345874999658115</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>23</v>
@@ -11093,7 +11099,9 @@
         <f t="shared" si="0"/>
         <v>57.457499999999712</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="13">
+        <v>94</v>
+      </c>
       <c r="G8" s="13">
         <f t="shared" si="1"/>
         <v>43295.799999999814</v>
@@ -11102,17 +11110,17 @@
         <f t="shared" si="2"/>
         <v>234663.23599999899</v>
       </c>
-      <c r="I8" s="12" t="e">
+      <c r="I8" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>460.59361702127461</v>
       </c>
       <c r="J8" s="14">
         <f t="shared" si="4"/>
         <v>0.17738654657790631</v>
       </c>
-      <c r="K8" s="15" t="e">
+      <c r="K8" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>7.0162488277644686</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>25</v>
@@ -11148,7 +11156,9 @@
         <f t="shared" si="0"/>
         <v>50.940759493671123</v>
       </c>
-      <c r="F9" s="13"/>
+      <c r="F9" s="13">
+        <v>94</v>
+      </c>
       <c r="G9" s="13">
         <f t="shared" si="1"/>
         <v>40012.799999999814</v>
@@ -11157,17 +11167,17 @@
         <f t="shared" si="2"/>
         <v>216869.375999999</v>
       </c>
-      <c r="I9" s="12" t="e">
+      <c r="I9" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>425.668085106381</v>
       </c>
       <c r="J9" s="14">
         <f t="shared" si="4"/>
         <v>-5.7251908397038869E-3</v>
       </c>
-      <c r="K9" s="15" t="e">
+      <c r="K9" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>7.3561393535812121</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>27</v>
@@ -11203,7 +11213,9 @@
         <f t="shared" si="0"/>
         <v>18.68800000000018</v>
       </c>
-      <c r="F10" s="13"/>
+      <c r="F10" s="13">
+        <v>94</v>
+      </c>
       <c r="G10" s="13">
         <f t="shared" si="1"/>
         <v>45390.400000000373</v>
@@ -11212,17 +11224,17 @@
         <f t="shared" si="2"/>
         <v>246015.968000002</v>
       </c>
-      <c r="I10" s="12" t="e">
+      <c r="I10" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>482.87659574468483</v>
       </c>
       <c r="J10" s="14">
         <f t="shared" si="4"/>
         <v>0.18480621450049936</v>
       </c>
-      <c r="K10" s="15" t="e">
+      <c r="K10" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>24.838858933255576</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>29</v>
@@ -11258,7 +11270,9 @@
         <f t="shared" si="0"/>
         <v>30.084904214559245</v>
       </c>
-      <c r="F11" s="13"/>
+      <c r="F11" s="13">
+        <v>94</v>
+      </c>
       <c r="G11" s="13">
         <f t="shared" si="1"/>
         <v>43975.200000000186</v>
@@ -11267,17 +11281,17 @@
         <f t="shared" si="2"/>
         <v>238345.58400000099</v>
       </c>
-      <c r="I11" s="12" t="e">
+      <c r="I11" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>467.82127659574667</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" si="4"/>
         <v>0.12007906104818024</v>
       </c>
-      <c r="K11" s="15" t="e">
+      <c r="K11" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>14.550033773062502</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>31</v>
@@ -11293,7 +11307,7 @@
         <v>43975.200000000186</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="24.95" customHeight="1" thickBot="1">
+    <row r="12" spans="1:16" ht="24.95" customHeight="1">
       <c r="A12" s="10" t="s">
         <v>32</v>
       </c>
@@ -11313,35 +11327,39 @@
         <f t="shared" si="0"/>
         <v>28.625454545454545</v>
       </c>
-      <c r="F12" s="13"/>
+      <c r="F12" s="13">
+        <v>94</v>
+      </c>
       <c r="G12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-8038867.2000000002</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="12" t="e">
+        <v>-43570660.223999999</v>
+      </c>
+      <c r="I12" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>-85519.863829787239</v>
       </c>
       <c r="J12" s="14">
         <f t="shared" si="4"/>
-        <v>-1</v>
-      </c>
-      <c r="K12" s="15" t="e">
+        <v>-205.23951219512196</v>
+      </c>
+      <c r="K12" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>-2988.5460560456672</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>33</v>
       </c>
       <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
+      <c r="O12" s="18">
+        <v>8038867.2000000002</v>
+      </c>
       <c r="P12" s="18">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-8038867.2000000002</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="24.95" customHeight="1" thickBot="1">
@@ -11364,7 +11382,9 @@
         <f t="shared" si="0"/>
         <v>33.450923694778666</v>
       </c>
-      <c r="F13" s="13"/>
+      <c r="F13" s="13">
+        <v>94</v>
+      </c>
       <c r="G13" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -11373,17 +11393,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="12" t="e">
+      <c r="I13" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="J13" s="14">
         <f t="shared" si="4"/>
         <v>-1</v>
       </c>
-      <c r="K13" s="15" t="e">
+      <c r="K13" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>35</v>
@@ -11415,7 +11435,9 @@
         <f t="shared" si="0"/>
         <v>32.876039603961132</v>
       </c>
-      <c r="F14" s="13"/>
+      <c r="F14" s="13">
+        <v>94</v>
+      </c>
       <c r="G14" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -11424,17 +11446,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="12" t="e">
+      <c r="I14" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="4"/>
         <v>-1</v>
       </c>
-      <c r="K14" s="15" t="e">
+      <c r="K14" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>37</v>
@@ -11466,7 +11488,9 @@
         <f t="shared" si="0"/>
         <v>38.914355828219946</v>
       </c>
-      <c r="F15" s="13"/>
+      <c r="F15" s="13">
+        <v>94</v>
+      </c>
       <c r="G15" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -11475,17 +11499,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I15" s="12" t="e">
+      <c r="I15" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="J15" s="14">
         <f t="shared" si="4"/>
         <v>-1</v>
       </c>
-      <c r="K15" s="15" t="e">
+      <c r="K15" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>39</v>
@@ -11517,7 +11541,9 @@
         <f t="shared" si="0"/>
         <v>24.760851063829985</v>
       </c>
-      <c r="F16" s="13"/>
+      <c r="F16" s="13">
+        <v>94</v>
+      </c>
       <c r="G16" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -11526,17 +11552,17 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I16" s="12" t="e">
+      <c r="I16" s="12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="J16" s="14">
         <f t="shared" si="4"/>
         <v>-1</v>
       </c>
-      <c r="K16" s="15" t="e">
+      <c r="K16" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>41</v>
@@ -11568,29 +11594,29 @@
         <f t="shared" si="7"/>
         <v>32.213285736401453</v>
       </c>
-      <c r="F17" s="12" t="e">
+      <c r="F17" s="12">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>94</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="7"/>
-        <v>22049.533333333366</v>
+        <v>-647856.06666666665</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="7"/>
-        <v>119508.47066666682</v>
-      </c>
-      <c r="I17" s="12" t="e">
+        <v>-3511379.881333333</v>
+      </c>
+      <c r="I17" s="12">
         <f>G17/F17</f>
-        <v>#DIV/0!</v>
+        <v>-6892.0858156028371</v>
       </c>
       <c r="J17" s="14">
         <f>(G17-C17)/C17</f>
-        <v>-0.34349816195444066</v>
-      </c>
-      <c r="K17" s="15" t="e">
+        <v>-20.289238104312069</v>
+      </c>
+      <c r="K17" s="15">
         <f>(I17-E17)/E17</f>
-        <v>#DIV/0!</v>
+        <v>-214.95165559949962</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="24.95" customHeight="1">
@@ -11615,27 +11641,27 @@
       </c>
       <c r="F18" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="8"/>
-        <v>264594.40000000037</v>
+        <v>-7774272.7999999998</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="8"/>
-        <v>1434101.6480000019</v>
-      </c>
-      <c r="I18" s="12" t="e">
+        <v>-42136558.575999998</v>
+      </c>
+      <c r="I18" s="12">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-82705.029787234045</v>
       </c>
       <c r="J18" s="14">
         <f>(G18-C18)/C18</f>
-        <v>-0.34349816195444066</v>
-      </c>
-      <c r="K18" s="15" t="e">
+        <v>-20.289238104312073</v>
+      </c>
+      <c r="K18" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>-214.95165559949965</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="21.75" customHeight="1">
@@ -11679,90 +11705,90 @@
     </row>
     <row r="40" spans="1:12" ht="21.95" customHeight="1"/>
     <row r="43" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A43" s="45" t="s">
+      <c r="A43" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="45"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="45"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
     </row>
     <row r="44" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A44" s="45"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="45"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="45"/>
+      <c r="A44" s="44"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
+      <c r="L44" s="44"/>
     </row>
     <row r="45" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A45" s="45"/>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="45"/>
+      <c r="A45" s="44"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="44"/>
     </row>
     <row r="46" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A46" s="45"/>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="45"/>
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="44"/>
     </row>
     <row r="47" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A47" s="45"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="45"/>
-      <c r="L47" s="45"/>
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
     </row>
     <row r="48" spans="1:12" ht="21.6" customHeight="1">
-      <c r="A48" s="45"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45"/>
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="44"/>
     </row>
     <row r="49" spans="1:12" ht="35.1" customHeight="1">
       <c r="A49" s="23"/>
@@ -11783,20 +11809,20 @@
       <c r="L49" s="23"/>
     </row>
     <row r="50" spans="1:12" ht="42" customHeight="1">
-      <c r="A50" s="41" t="s">
+      <c r="A50" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
     </row>
     <row r="51" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
       <c r="A51" s="26" t="s">
@@ -12714,41 +12740,41 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:17" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:17" s="6" customFormat="1" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44" t="s">
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="44"/>
+      <c r="K3" s="43"/>
       <c r="N3" s="7" t="s">
         <v>6</v>
       </c>
@@ -12757,7 +12783,7 @@
       <c r="Q3" s="8"/>
     </row>
     <row r="4" spans="1:17" s="6" customFormat="1" ht="54" customHeight="1" thickBot="1">
-      <c r="A4" s="43"/>
+      <c r="A4" s="42"/>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -13600,106 +13626,106 @@
     </row>
     <row r="40" spans="1:12" ht="21.95" customHeight="1"/>
     <row r="45" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A45" s="53" t="s">
+      <c r="A45" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="53"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
-      <c r="F45" s="53"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="53"/>
-      <c r="I45" s="53"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="53"/>
-      <c r="L45" s="53"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
     </row>
     <row r="46" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A46" s="53"/>
-      <c r="B46" s="53"/>
-      <c r="C46" s="53"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="53"/>
-      <c r="G46" s="53"/>
-      <c r="H46" s="53"/>
-      <c r="I46" s="53"/>
-      <c r="J46" s="53"/>
-      <c r="K46" s="53"/>
-      <c r="L46" s="53"/>
+      <c r="A46" s="52"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="52"/>
     </row>
     <row r="47" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A47" s="53"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="53"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="53"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="53"/>
-      <c r="L47" s="53"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="52"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="52"/>
     </row>
     <row r="48" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A48" s="53"/>
-      <c r="B48" s="53"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="53"/>
-      <c r="G48" s="53"/>
-      <c r="H48" s="53"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
+      <c r="A48" s="52"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
+      <c r="K48" s="52"/>
+      <c r="L48" s="52"/>
     </row>
     <row r="49" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A49" s="53"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="53"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
+      <c r="A49" s="52"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="52"/>
+      <c r="K49" s="52"/>
+      <c r="L49" s="52"/>
     </row>
     <row r="50" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A50" s="53"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="53"/>
-      <c r="I50" s="53"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="53"/>
+      <c r="A50" s="52"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="52"/>
+      <c r="K50" s="52"/>
+      <c r="L50" s="52"/>
     </row>
     <row r="51" spans="1:12" ht="42" customHeight="1">
-      <c r="A51" s="52" t="s">
+      <c r="A51" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="52"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="52"/>
-      <c r="K51" s="52"/>
-      <c r="L51" s="52"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
     </row>
     <row r="52" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
       <c r="A52" s="46" t="s">

--- a/data/staging/source/1.2electric.xlsx
+++ b/data/staging/source/1.2electric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maejo365-my.sharepoint.com/personal/researchmju_mju_ac_th/Documents/RAE-Document-Center/07-GreenOffice/resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{B123507F-AE86-4D30-ACF2-EB8587520D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C2FB205-55A4-48B6-9080-053FA4954495}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{B123507F-AE86-4D30-ACF2-EB8587520D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B49EF2D6-495F-4705-ABAC-DE2A7DDBD4B8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{150D84F5-2079-49F3-B53F-3CC6B2C0B5A9}"/>
   </bookViews>
@@ -764,9 +764,6 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -782,29 +779,32 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10292,7 +10292,9 @@
     <col min="4" max="4" width="12.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="11" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.5" style="3" customWidth="1"/>
-    <col min="7" max="9" width="11" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11" style="3" customWidth="1"/>
     <col min="10" max="10" width="11.375" style="3" customWidth="1"/>
     <col min="11" max="11" width="13.875" style="3" customWidth="1"/>
     <col min="12" max="12" width="9" style="3"/>
@@ -10823,41 +10825,41 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:16" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:16" s="6" customFormat="1" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43" t="s">
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43" t="s">
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="43"/>
+      <c r="K3" s="42"/>
       <c r="M3" s="7" t="s">
         <v>6</v>
       </c>
@@ -10866,7 +10868,7 @@
       <c r="P3" s="8"/>
     </row>
     <row r="4" spans="1:16" s="6" customFormat="1" ht="54" customHeight="1" thickBot="1">
-      <c r="A4" s="42"/>
+      <c r="A4" s="41"/>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -11705,90 +11707,90 @@
     </row>
     <row r="40" spans="1:12" ht="21.95" customHeight="1"/>
     <row r="43" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A43" s="44" t="s">
+      <c r="A43" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="44"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="44"/>
-      <c r="L43" s="44"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="43"/>
     </row>
     <row r="44" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A44" s="44"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="44"/>
-      <c r="L44" s="44"/>
+      <c r="A44" s="43"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+      <c r="L44" s="43"/>
     </row>
     <row r="45" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A45" s="44"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="44"/>
-      <c r="K45" s="44"/>
-      <c r="L45" s="44"/>
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="43"/>
     </row>
     <row r="46" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A46" s="44"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="44"/>
-      <c r="L46" s="44"/>
+      <c r="A46" s="43"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="43"/>
     </row>
     <row r="47" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A47" s="44"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="44"/>
-      <c r="L47" s="44"/>
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="43"/>
     </row>
     <row r="48" spans="1:12" ht="21.6" customHeight="1">
-      <c r="A48" s="44"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="44"/>
-      <c r="L48" s="44"/>
+      <c r="A48" s="43"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+      <c r="L48" s="43"/>
     </row>
     <row r="49" spans="1:12" ht="35.1" customHeight="1">
       <c r="A49" s="23"/>
@@ -11809,20 +11811,20 @@
       <c r="L49" s="23"/>
     </row>
     <row r="50" spans="1:12" ht="42" customHeight="1">
-      <c r="A50" s="45" t="s">
+      <c r="A50" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
     </row>
     <row r="51" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
       <c r="A51" s="26" t="s">
@@ -11861,10 +11863,10 @@
       <c r="L52" s="30"/>
     </row>
     <row r="53" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B53" s="40"/>
+      <c r="B53" s="45"/>
       <c r="C53" s="31"/>
       <c r="D53" s="32"/>
       <c r="E53" s="30"/>
@@ -11929,10 +11931,10 @@
       <c r="L56" s="30"/>
     </row>
     <row r="57" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A57" s="40" t="s">
+      <c r="A57" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="40"/>
+      <c r="B57" s="45"/>
       <c r="C57" s="31"/>
       <c r="D57" s="32"/>
       <c r="E57" s="30"/>
@@ -12269,10 +12271,10 @@
       <c r="L76" s="30"/>
     </row>
     <row r="77" spans="1:12" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A77" s="40" t="s">
+      <c r="A77" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B77" s="40"/>
+      <c r="B77" s="45"/>
       <c r="C77" s="31"/>
       <c r="D77" s="32"/>
       <c r="E77" s="30"/>
@@ -12337,10 +12339,10 @@
       <c r="L80" s="30"/>
     </row>
     <row r="81" spans="1:19" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A81" s="40" t="s">
+      <c r="A81" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B81" s="40"/>
+      <c r="B81" s="45"/>
       <c r="C81" s="31"/>
       <c r="D81" s="32"/>
       <c r="E81" s="30"/>
@@ -12669,6 +12671,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A93:B93"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:A4"/>
@@ -12681,13 +12690,6 @@
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A93:B93"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.18" top="0.28999999999999998" bottom="0.18" header="0.24" footer="0.08"/>
   <pageSetup paperSize="9" scale="68" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId1"/>
@@ -12740,41 +12742,41 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:17" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:17" s="6" customFormat="1" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43" t="s">
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43" t="s">
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="43"/>
+      <c r="K3" s="42"/>
       <c r="N3" s="7" t="s">
         <v>6</v>
       </c>
@@ -12783,7 +12785,7 @@
       <c r="Q3" s="8"/>
     </row>
     <row r="4" spans="1:17" s="6" customFormat="1" ht="54" customHeight="1" thickBot="1">
-      <c r="A4" s="42"/>
+      <c r="A4" s="41"/>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -13626,700 +13628,700 @@
     </row>
     <row r="40" spans="1:12" ht="21.95" customHeight="1"/>
     <row r="45" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A45" s="52" t="s">
+      <c r="A45" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="52"/>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="52"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="47"/>
+      <c r="K45" s="47"/>
+      <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A46" s="52"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="52"/>
+      <c r="A46" s="47"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="47"/>
+      <c r="K46" s="47"/>
+      <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A47" s="52"/>
-      <c r="B47" s="52"/>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="52"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
-      <c r="L47" s="52"/>
+      <c r="A47" s="47"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="47"/>
+      <c r="K47" s="47"/>
+      <c r="L47" s="47"/>
     </row>
     <row r="48" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A48" s="52"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="52"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="52"/>
-      <c r="L48" s="52"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="47"/>
+      <c r="K48" s="47"/>
+      <c r="L48" s="47"/>
     </row>
     <row r="49" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A49" s="52"/>
-      <c r="B49" s="52"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="52"/>
-      <c r="H49" s="52"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="52"/>
-      <c r="K49" s="52"/>
-      <c r="L49" s="52"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="47"/>
+      <c r="K49" s="47"/>
+      <c r="L49" s="47"/>
     </row>
     <row r="50" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A50" s="52"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="52"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="52"/>
-      <c r="J50" s="52"/>
-      <c r="K50" s="52"/>
-      <c r="L50" s="52"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="47"/>
+      <c r="K50" s="47"/>
+      <c r="L50" s="47"/>
     </row>
     <row r="51" spans="1:12" ht="42" customHeight="1">
-      <c r="A51" s="53" t="s">
+      <c r="A51" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="53"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="53"/>
-      <c r="L51" s="53"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
+      <c r="L51" s="48"/>
     </row>
     <row r="52" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A52" s="46" t="s">
+      <c r="A52" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="B52" s="46"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="49"/>
+      <c r="H52" s="49"/>
+      <c r="I52" s="49"/>
+      <c r="J52" s="49"/>
+      <c r="K52" s="49"/>
+      <c r="L52" s="49"/>
     </row>
     <row r="53" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A53" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B53" s="38"/>
-      <c r="C53" s="47" t="s">
+      <c r="C53" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="D53" s="47"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="47"/>
-      <c r="I53" s="47"/>
-      <c r="J53" s="47"/>
-      <c r="K53" s="47"/>
-      <c r="L53" s="47"/>
+      <c r="D53" s="50"/>
+      <c r="E53" s="50"/>
+      <c r="F53" s="50"/>
+      <c r="G53" s="50"/>
+      <c r="H53" s="50"/>
+      <c r="I53" s="50"/>
+      <c r="J53" s="50"/>
+      <c r="K53" s="50"/>
+      <c r="L53" s="50"/>
     </row>
     <row r="54" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A54" s="49" t="s">
+      <c r="A54" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="49"/>
-      <c r="C54" s="48" t="s">
+      <c r="B54" s="51"/>
+      <c r="C54" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="48"/>
-      <c r="J54" s="48"/>
-      <c r="K54" s="48"/>
-      <c r="L54" s="48"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="46"/>
+      <c r="I54" s="46"/>
+      <c r="J54" s="46"/>
+      <c r="K54" s="46"/>
+      <c r="L54" s="46"/>
     </row>
     <row r="55" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A55" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B55" s="38"/>
-      <c r="C55" s="48" t="s">
+      <c r="C55" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="48"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="48"/>
-      <c r="L55" s="48"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
+      <c r="L55" s="46"/>
     </row>
     <row r="56" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A56" s="46" t="s">
+      <c r="A56" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="B56" s="46"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
-      <c r="L56" s="46"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="49"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
+      <c r="L56" s="49"/>
     </row>
     <row r="57" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A57" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B57" s="38"/>
-      <c r="C57" s="47" t="s">
+      <c r="C57" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="47"/>
-      <c r="H57" s="47"/>
-      <c r="I57" s="47"/>
-      <c r="J57" s="47"/>
-      <c r="K57" s="47"/>
-      <c r="L57" s="47"/>
+      <c r="D57" s="50"/>
+      <c r="E57" s="50"/>
+      <c r="F57" s="50"/>
+      <c r="G57" s="50"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="50"/>
+      <c r="J57" s="50"/>
+      <c r="K57" s="50"/>
+      <c r="L57" s="50"/>
     </row>
     <row r="58" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A58" s="49" t="s">
+      <c r="A58" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B58" s="49"/>
-      <c r="C58" s="48" t="s">
+      <c r="B58" s="51"/>
+      <c r="C58" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="48"/>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
-      <c r="L58" s="48"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="46"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="46"/>
+      <c r="K58" s="46"/>
+      <c r="L58" s="46"/>
     </row>
     <row r="59" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A59" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B59" s="38"/>
-      <c r="C59" s="48" t="s">
+      <c r="C59" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
-      <c r="L59" s="48"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="46"/>
+      <c r="G59" s="46"/>
+      <c r="H59" s="46"/>
+      <c r="I59" s="46"/>
+      <c r="J59" s="46"/>
+      <c r="K59" s="46"/>
+      <c r="L59" s="46"/>
     </row>
     <row r="60" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A60" s="46" t="s">
+      <c r="A60" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="B60" s="46"/>
-      <c r="C60" s="46"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="49"/>
+      <c r="J60" s="49"/>
+      <c r="K60" s="49"/>
+      <c r="L60" s="49"/>
     </row>
     <row r="61" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A61" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B61" s="38"/>
-      <c r="C61" s="47" t="s">
+      <c r="C61" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="D61" s="47"/>
-      <c r="E61" s="47"/>
-      <c r="F61" s="47"/>
-      <c r="G61" s="47"/>
-      <c r="H61" s="47"/>
-      <c r="I61" s="47"/>
-      <c r="J61" s="47"/>
-      <c r="K61" s="47"/>
-      <c r="L61" s="47"/>
+      <c r="D61" s="50"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="50"/>
+      <c r="G61" s="50"/>
+      <c r="H61" s="50"/>
+      <c r="I61" s="50"/>
+      <c r="J61" s="50"/>
+      <c r="K61" s="50"/>
+      <c r="L61" s="50"/>
     </row>
     <row r="62" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A62" s="47" t="s">
+      <c r="A62" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B62" s="47"/>
-      <c r="C62" s="51" t="s">
+      <c r="B62" s="50"/>
+      <c r="C62" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="D62" s="51"/>
-      <c r="E62" s="51"/>
-      <c r="F62" s="51"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="51"/>
-      <c r="I62" s="51"/>
-      <c r="J62" s="51"/>
-      <c r="K62" s="51"/>
-      <c r="L62" s="51"/>
+      <c r="D62" s="52"/>
+      <c r="E62" s="52"/>
+      <c r="F62" s="52"/>
+      <c r="G62" s="52"/>
+      <c r="H62" s="52"/>
+      <c r="I62" s="52"/>
+      <c r="J62" s="52"/>
+      <c r="K62" s="52"/>
+      <c r="L62" s="52"/>
     </row>
     <row r="63" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A63" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B63" s="38"/>
-      <c r="C63" s="48" t="s">
+      <c r="C63" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D63" s="48"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
-      <c r="L63" s="48"/>
+      <c r="D63" s="46"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="46"/>
+      <c r="G63" s="46"/>
+      <c r="H63" s="46"/>
+      <c r="I63" s="46"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="46"/>
+      <c r="L63" s="46"/>
     </row>
     <row r="64" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A64" s="46" t="s">
+      <c r="A64" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="46"/>
-      <c r="C64" s="46"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="46"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="46"/>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="46"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="49"/>
+      <c r="D64" s="49"/>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="49"/>
+      <c r="H64" s="49"/>
+      <c r="I64" s="49"/>
+      <c r="J64" s="49"/>
+      <c r="K64" s="49"/>
+      <c r="L64" s="49"/>
     </row>
     <row r="65" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A65" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B65" s="38"/>
-      <c r="C65" s="47" t="s">
+      <c r="C65" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="D65" s="47"/>
-      <c r="E65" s="47"/>
-      <c r="F65" s="47"/>
-      <c r="G65" s="47"/>
-      <c r="H65" s="47"/>
-      <c r="I65" s="47"/>
-      <c r="J65" s="47"/>
-      <c r="K65" s="47"/>
-      <c r="L65" s="47"/>
+      <c r="D65" s="50"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
+      <c r="H65" s="50"/>
+      <c r="I65" s="50"/>
+      <c r="J65" s="50"/>
+      <c r="K65" s="50"/>
+      <c r="L65" s="50"/>
     </row>
     <row r="66" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A66" s="47" t="s">
+      <c r="A66" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B66" s="47"/>
-      <c r="C66" s="48" t="s">
+      <c r="B66" s="50"/>
+      <c r="C66" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="D66" s="48"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48"/>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
-      <c r="L66" s="48"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="46"/>
+      <c r="H66" s="46"/>
+      <c r="I66" s="46"/>
+      <c r="J66" s="46"/>
+      <c r="K66" s="46"/>
+      <c r="L66" s="46"/>
     </row>
     <row r="67" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A67" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B67" s="38"/>
-      <c r="C67" s="48" t="s">
+      <c r="C67" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="D67" s="48"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="48"/>
-      <c r="H67" s="48"/>
-      <c r="I67" s="48"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
-      <c r="L67" s="48"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="46"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="46"/>
+      <c r="I67" s="46"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="46"/>
+      <c r="L67" s="46"/>
     </row>
     <row r="68" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A68" s="46" t="s">
+      <c r="A68" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B68" s="46"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="46"/>
-      <c r="J68" s="46"/>
-      <c r="K68" s="46"/>
-      <c r="L68" s="46"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="49"/>
+      <c r="D68" s="49"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="49"/>
+      <c r="J68" s="49"/>
+      <c r="K68" s="49"/>
+      <c r="L68" s="49"/>
     </row>
     <row r="69" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A69" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B69" s="38"/>
-      <c r="C69" s="47" t="s">
+      <c r="C69" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="47"/>
-      <c r="J69" s="47"/>
-      <c r="K69" s="47"/>
-      <c r="L69" s="47"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
+      <c r="H69" s="50"/>
+      <c r="I69" s="50"/>
+      <c r="J69" s="50"/>
+      <c r="K69" s="50"/>
+      <c r="L69" s="50"/>
     </row>
     <row r="70" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A70" s="47" t="s">
+      <c r="A70" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B70" s="47"/>
-      <c r="C70" s="48" t="s">
+      <c r="B70" s="50"/>
+      <c r="C70" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="48"/>
-      <c r="L70" s="48"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="46"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="46"/>
+      <c r="I70" s="46"/>
+      <c r="J70" s="46"/>
+      <c r="K70" s="46"/>
+      <c r="L70" s="46"/>
     </row>
     <row r="71" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A71" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B71" s="38"/>
-      <c r="C71" s="48" t="s">
+      <c r="C71" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
-      <c r="J71" s="48"/>
-      <c r="K71" s="48"/>
-      <c r="L71" s="48"/>
+      <c r="D71" s="46"/>
+      <c r="E71" s="46"/>
+      <c r="F71" s="46"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="46"/>
+      <c r="I71" s="46"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="46"/>
+      <c r="L71" s="46"/>
     </row>
     <row r="72" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A72" s="46" t="s">
+      <c r="A72" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="B72" s="46"/>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46"/>
-      <c r="L72" s="46"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="49"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="49"/>
+      <c r="J72" s="49"/>
+      <c r="K72" s="49"/>
+      <c r="L72" s="49"/>
     </row>
     <row r="73" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A73" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B73" s="38"/>
-      <c r="C73" s="47" t="s">
+      <c r="C73" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D73" s="47"/>
-      <c r="E73" s="47"/>
-      <c r="F73" s="47"/>
-      <c r="G73" s="47"/>
-      <c r="H73" s="47"/>
-      <c r="I73" s="47"/>
-      <c r="J73" s="47"/>
-      <c r="K73" s="47"/>
-      <c r="L73" s="47"/>
+      <c r="D73" s="50"/>
+      <c r="E73" s="50"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="50"/>
+      <c r="H73" s="50"/>
+      <c r="I73" s="50"/>
+      <c r="J73" s="50"/>
+      <c r="K73" s="50"/>
+      <c r="L73" s="50"/>
     </row>
     <row r="74" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A74" s="47" t="s">
+      <c r="A74" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B74" s="47"/>
-      <c r="C74" s="50" t="s">
+      <c r="B74" s="50"/>
+      <c r="C74" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="D74" s="50"/>
-      <c r="E74" s="50"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="50"/>
-      <c r="H74" s="50"/>
-      <c r="I74" s="50"/>
-      <c r="J74" s="50"/>
-      <c r="K74" s="50"/>
-      <c r="L74" s="50"/>
+      <c r="D74" s="53"/>
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="53"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+      <c r="L74" s="53"/>
     </row>
     <row r="75" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A75" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B75" s="38"/>
-      <c r="C75" s="48" t="s">
+      <c r="C75" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
-      <c r="L75" s="48"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="46"/>
+      <c r="F75" s="46"/>
+      <c r="G75" s="46"/>
+      <c r="H75" s="46"/>
+      <c r="I75" s="46"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="46"/>
+      <c r="L75" s="46"/>
     </row>
     <row r="76" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A76" s="46" t="s">
+      <c r="A76" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="B76" s="46"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
-      <c r="J76" s="46"/>
-      <c r="K76" s="46"/>
-      <c r="L76" s="46"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
+      <c r="L76" s="49"/>
     </row>
     <row r="77" spans="1:12" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A77" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B77" s="38"/>
-      <c r="C77" s="47" t="s">
+      <c r="C77" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="47"/>
-      <c r="E77" s="47"/>
-      <c r="F77" s="47"/>
-      <c r="G77" s="47"/>
-      <c r="H77" s="47"/>
-      <c r="I77" s="47"/>
-      <c r="J77" s="47"/>
-      <c r="K77" s="47"/>
-      <c r="L77" s="47"/>
+      <c r="D77" s="50"/>
+      <c r="E77" s="50"/>
+      <c r="F77" s="50"/>
+      <c r="G77" s="50"/>
+      <c r="H77" s="50"/>
+      <c r="I77" s="50"/>
+      <c r="J77" s="50"/>
+      <c r="K77" s="50"/>
+      <c r="L77" s="50"/>
     </row>
     <row r="78" spans="1:12" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A78" s="49" t="s">
+      <c r="A78" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B78" s="49"/>
-      <c r="C78" s="48" t="s">
+      <c r="B78" s="51"/>
+      <c r="C78" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="48"/>
-      <c r="L78" s="48"/>
+      <c r="D78" s="46"/>
+      <c r="E78" s="46"/>
+      <c r="F78" s="46"/>
+      <c r="G78" s="46"/>
+      <c r="H78" s="46"/>
+      <c r="I78" s="46"/>
+      <c r="J78" s="46"/>
+      <c r="K78" s="46"/>
+      <c r="L78" s="46"/>
     </row>
     <row r="79" spans="1:12" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A79" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B79" s="38"/>
-      <c r="C79" s="48" t="s">
+      <c r="C79" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="48"/>
-      <c r="L79" s="48"/>
+      <c r="D79" s="46"/>
+      <c r="E79" s="46"/>
+      <c r="F79" s="46"/>
+      <c r="G79" s="46"/>
+      <c r="H79" s="46"/>
+      <c r="I79" s="46"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
+      <c r="L79" s="46"/>
     </row>
     <row r="80" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A80" s="46" t="s">
+      <c r="A80" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="46"/>
-      <c r="C80" s="46"/>
-      <c r="D80" s="46"/>
-      <c r="E80" s="46"/>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
-      <c r="L80" s="46"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
+      <c r="J80" s="49"/>
+      <c r="K80" s="49"/>
+      <c r="L80" s="49"/>
     </row>
     <row r="81" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A81" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B81" s="38"/>
-      <c r="C81" s="47" t="s">
+      <c r="C81" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D81" s="47"/>
-      <c r="E81" s="47"/>
-      <c r="F81" s="47"/>
-      <c r="G81" s="47"/>
-      <c r="H81" s="47"/>
-      <c r="I81" s="47"/>
-      <c r="J81" s="47"/>
-      <c r="K81" s="47"/>
-      <c r="L81" s="47"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="50"/>
+      <c r="I81" s="50"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="50"/>
+      <c r="L81" s="50"/>
     </row>
     <row r="82" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A82" s="49" t="s">
+      <c r="A82" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B82" s="49"/>
-      <c r="C82" s="48" t="s">
+      <c r="B82" s="51"/>
+      <c r="C82" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="D82" s="48"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="48"/>
-      <c r="G82" s="48"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48"/>
-      <c r="J82" s="48"/>
-      <c r="K82" s="48"/>
-      <c r="L82" s="48"/>
+      <c r="D82" s="46"/>
+      <c r="E82" s="46"/>
+      <c r="F82" s="46"/>
+      <c r="G82" s="46"/>
+      <c r="H82" s="46"/>
+      <c r="I82" s="46"/>
+      <c r="J82" s="46"/>
+      <c r="K82" s="46"/>
+      <c r="L82" s="46"/>
     </row>
     <row r="83" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A83" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B83" s="38"/>
-      <c r="C83" s="48" t="s">
+      <c r="C83" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D83" s="48"/>
-      <c r="E83" s="48"/>
-      <c r="F83" s="48"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="48"/>
-      <c r="J83" s="48"/>
-      <c r="K83" s="48"/>
-      <c r="L83" s="48"/>
+      <c r="D83" s="46"/>
+      <c r="E83" s="46"/>
+      <c r="F83" s="46"/>
+      <c r="G83" s="46"/>
+      <c r="H83" s="46"/>
+      <c r="I83" s="46"/>
+      <c r="J83" s="46"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="46"/>
     </row>
     <row r="84" spans="1:20" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A84" s="46" t="s">
+      <c r="A84" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="B84" s="46"/>
-      <c r="C84" s="46"/>
-      <c r="D84" s="46"/>
-      <c r="E84" s="46"/>
-      <c r="F84" s="46"/>
-      <c r="G84" s="46"/>
-      <c r="H84" s="46"/>
-      <c r="I84" s="46"/>
-      <c r="J84" s="46"/>
-      <c r="K84" s="46"/>
-      <c r="L84" s="46"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="49"/>
+      <c r="E84" s="49"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="49"/>
+      <c r="H84" s="49"/>
+      <c r="I84" s="49"/>
+      <c r="J84" s="49"/>
+      <c r="K84" s="49"/>
+      <c r="L84" s="49"/>
     </row>
     <row r="85" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A85" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B85" s="38"/>
-      <c r="C85" s="47" t="s">
+      <c r="C85" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="D85" s="47"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="47"/>
-      <c r="G85" s="47"/>
-      <c r="H85" s="47"/>
-      <c r="I85" s="47"/>
-      <c r="J85" s="47"/>
-      <c r="K85" s="47"/>
-      <c r="L85" s="47"/>
+      <c r="D85" s="50"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
+      <c r="H85" s="50"/>
+      <c r="I85" s="50"/>
+      <c r="J85" s="50"/>
+      <c r="K85" s="50"/>
+      <c r="L85" s="50"/>
       <c r="M85" s="34"/>
       <c r="N85" s="34"/>
       <c r="O85" s="34"/>
@@ -14330,22 +14332,22 @@
       <c r="T85" s="34"/>
     </row>
     <row r="86" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A86" s="47" t="s">
+      <c r="A86" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B86" s="47"/>
-      <c r="C86" s="48" t="s">
+      <c r="B86" s="50"/>
+      <c r="C86" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
-      <c r="J86" s="48"/>
-      <c r="K86" s="48"/>
-      <c r="L86" s="48"/>
+      <c r="D86" s="46"/>
+      <c r="E86" s="46"/>
+      <c r="F86" s="46"/>
+      <c r="G86" s="46"/>
+      <c r="H86" s="46"/>
+      <c r="I86" s="46"/>
+      <c r="J86" s="46"/>
+      <c r="K86" s="46"/>
+      <c r="L86" s="46"/>
       <c r="M86" s="34"/>
       <c r="N86" s="34"/>
       <c r="O86" s="34"/>
@@ -14360,18 +14362,18 @@
         <v>51</v>
       </c>
       <c r="B87" s="38"/>
-      <c r="C87" s="48" t="s">
+      <c r="C87" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
-      <c r="J87" s="48"/>
-      <c r="K87" s="48"/>
-      <c r="L87" s="48"/>
+      <c r="D87" s="46"/>
+      <c r="E87" s="46"/>
+      <c r="F87" s="46"/>
+      <c r="G87" s="46"/>
+      <c r="H87" s="46"/>
+      <c r="I87" s="46"/>
+      <c r="J87" s="46"/>
+      <c r="K87" s="46"/>
+      <c r="L87" s="46"/>
       <c r="M87" s="34"/>
       <c r="N87" s="34"/>
       <c r="O87" s="34"/>
@@ -14382,214 +14384,214 @@
       <c r="T87" s="34"/>
     </row>
     <row r="88" spans="1:20" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A88" s="46" t="s">
+      <c r="A88" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="46"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="46"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="46"/>
-      <c r="J88" s="46"/>
-      <c r="K88" s="46"/>
-      <c r="L88" s="46"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
+      <c r="J88" s="49"/>
+      <c r="K88" s="49"/>
+      <c r="L88" s="49"/>
     </row>
     <row r="89" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A89" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B89" s="38"/>
-      <c r="C89" s="47" t="s">
+      <c r="C89" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="D89" s="47"/>
-      <c r="E89" s="47"/>
-      <c r="F89" s="47"/>
-      <c r="G89" s="47"/>
-      <c r="H89" s="47"/>
-      <c r="I89" s="47"/>
-      <c r="J89" s="47"/>
-      <c r="K89" s="47"/>
-      <c r="L89" s="47"/>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
+      <c r="H89" s="50"/>
+      <c r="I89" s="50"/>
+      <c r="J89" s="50"/>
+      <c r="K89" s="50"/>
+      <c r="L89" s="50"/>
     </row>
     <row r="90" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A90" s="47" t="s">
+      <c r="A90" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B90" s="47"/>
-      <c r="C90" s="48" t="s">
+      <c r="B90" s="50"/>
+      <c r="C90" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="D90" s="48"/>
-      <c r="E90" s="48"/>
-      <c r="F90" s="48"/>
-      <c r="G90" s="48"/>
-      <c r="H90" s="48"/>
-      <c r="I90" s="48"/>
-      <c r="J90" s="48"/>
-      <c r="K90" s="48"/>
-      <c r="L90" s="48"/>
+      <c r="D90" s="46"/>
+      <c r="E90" s="46"/>
+      <c r="F90" s="46"/>
+      <c r="G90" s="46"/>
+      <c r="H90" s="46"/>
+      <c r="I90" s="46"/>
+      <c r="J90" s="46"/>
+      <c r="K90" s="46"/>
+      <c r="L90" s="46"/>
     </row>
     <row r="91" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A91" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B91" s="38"/>
-      <c r="C91" s="48" t="s">
+      <c r="C91" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D91" s="48"/>
-      <c r="E91" s="48"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="48"/>
-      <c r="H91" s="48"/>
-      <c r="I91" s="48"/>
-      <c r="J91" s="48"/>
-      <c r="K91" s="48"/>
-      <c r="L91" s="48"/>
+      <c r="D91" s="46"/>
+      <c r="E91" s="46"/>
+      <c r="F91" s="46"/>
+      <c r="G91" s="46"/>
+      <c r="H91" s="46"/>
+      <c r="I91" s="46"/>
+      <c r="J91" s="46"/>
+      <c r="K91" s="46"/>
+      <c r="L91" s="46"/>
     </row>
     <row r="92" spans="1:20" s="35" customFormat="1" ht="30" customHeight="1">
-      <c r="A92" s="46" t="s">
+      <c r="A92" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="B92" s="46"/>
-      <c r="C92" s="46"/>
-      <c r="D92" s="46"/>
-      <c r="E92" s="46"/>
-      <c r="F92" s="46"/>
-      <c r="G92" s="46"/>
-      <c r="H92" s="46"/>
-      <c r="I92" s="46"/>
-      <c r="J92" s="46"/>
-      <c r="K92" s="46"/>
-      <c r="L92" s="46"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="49"/>
+      <c r="D92" s="49"/>
+      <c r="E92" s="49"/>
+      <c r="F92" s="49"/>
+      <c r="G92" s="49"/>
+      <c r="H92" s="49"/>
+      <c r="I92" s="49"/>
+      <c r="J92" s="49"/>
+      <c r="K92" s="49"/>
+      <c r="L92" s="49"/>
     </row>
     <row r="93" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A93" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B93" s="38"/>
-      <c r="C93" s="47" t="s">
+      <c r="C93" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="D93" s="47"/>
-      <c r="E93" s="47"/>
-      <c r="F93" s="47"/>
-      <c r="G93" s="47"/>
-      <c r="H93" s="47"/>
-      <c r="I93" s="47"/>
-      <c r="J93" s="47"/>
-      <c r="K93" s="47"/>
-      <c r="L93" s="47"/>
+      <c r="D93" s="50"/>
+      <c r="E93" s="50"/>
+      <c r="F93" s="50"/>
+      <c r="G93" s="50"/>
+      <c r="H93" s="50"/>
+      <c r="I93" s="50"/>
+      <c r="J93" s="50"/>
+      <c r="K93" s="50"/>
+      <c r="L93" s="50"/>
     </row>
     <row r="94" spans="1:20" s="35" customFormat="1" ht="81" customHeight="1">
-      <c r="A94" s="47" t="s">
+      <c r="A94" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B94" s="47"/>
-      <c r="C94" s="48" t="s">
+      <c r="B94" s="50"/>
+      <c r="C94" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="D94" s="48"/>
-      <c r="E94" s="48"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="48"/>
-      <c r="H94" s="48"/>
-      <c r="I94" s="48"/>
-      <c r="J94" s="48"/>
-      <c r="K94" s="48"/>
-      <c r="L94" s="48"/>
+      <c r="D94" s="46"/>
+      <c r="E94" s="46"/>
+      <c r="F94" s="46"/>
+      <c r="G94" s="46"/>
+      <c r="H94" s="46"/>
+      <c r="I94" s="46"/>
+      <c r="J94" s="46"/>
+      <c r="K94" s="46"/>
+      <c r="L94" s="46"/>
     </row>
     <row r="95" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A95" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B95" s="38"/>
-      <c r="C95" s="48" t="s">
+      <c r="C95" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D95" s="48"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="48"/>
-      <c r="H95" s="48"/>
-      <c r="I95" s="48"/>
-      <c r="J95" s="48"/>
-      <c r="K95" s="48"/>
-      <c r="L95" s="48"/>
+      <c r="D95" s="46"/>
+      <c r="E95" s="46"/>
+      <c r="F95" s="46"/>
+      <c r="G95" s="46"/>
+      <c r="H95" s="46"/>
+      <c r="I95" s="46"/>
+      <c r="J95" s="46"/>
+      <c r="K95" s="46"/>
+      <c r="L95" s="46"/>
     </row>
     <row r="96" spans="1:20" s="35" customFormat="1" ht="30" customHeight="1">
-      <c r="A96" s="46" t="s">
+      <c r="A96" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="B96" s="46"/>
-      <c r="C96" s="46"/>
-      <c r="D96" s="46"/>
-      <c r="E96" s="46"/>
-      <c r="F96" s="46"/>
-      <c r="G96" s="46"/>
-      <c r="H96" s="46"/>
-      <c r="I96" s="46"/>
-      <c r="J96" s="46"/>
-      <c r="K96" s="46"/>
-      <c r="L96" s="46"/>
+      <c r="B96" s="49"/>
+      <c r="C96" s="49"/>
+      <c r="D96" s="49"/>
+      <c r="E96" s="49"/>
+      <c r="F96" s="49"/>
+      <c r="G96" s="49"/>
+      <c r="H96" s="49"/>
+      <c r="I96" s="49"/>
+      <c r="J96" s="49"/>
+      <c r="K96" s="49"/>
+      <c r="L96" s="49"/>
     </row>
     <row r="97" spans="1:12" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A97" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B97" s="38"/>
-      <c r="C97" s="47" t="s">
+      <c r="C97" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="D97" s="47"/>
-      <c r="E97" s="47"/>
-      <c r="F97" s="47"/>
-      <c r="G97" s="47"/>
-      <c r="H97" s="47"/>
-      <c r="I97" s="47"/>
-      <c r="J97" s="47"/>
-      <c r="K97" s="47"/>
-      <c r="L97" s="47"/>
+      <c r="D97" s="50"/>
+      <c r="E97" s="50"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50"/>
+      <c r="H97" s="50"/>
+      <c r="I97" s="50"/>
+      <c r="J97" s="50"/>
+      <c r="K97" s="50"/>
+      <c r="L97" s="50"/>
     </row>
     <row r="98" spans="1:12" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A98" s="47" t="s">
+      <c r="A98" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B98" s="47"/>
-      <c r="C98" s="48" t="s">
+      <c r="B98" s="50"/>
+      <c r="C98" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="D98" s="48"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="48"/>
-      <c r="I98" s="48"/>
-      <c r="J98" s="48"/>
-      <c r="K98" s="48"/>
-      <c r="L98" s="48"/>
+      <c r="D98" s="46"/>
+      <c r="E98" s="46"/>
+      <c r="F98" s="46"/>
+      <c r="G98" s="46"/>
+      <c r="H98" s="46"/>
+      <c r="I98" s="46"/>
+      <c r="J98" s="46"/>
+      <c r="K98" s="46"/>
+      <c r="L98" s="46"/>
     </row>
     <row r="99" spans="1:12" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A99" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B99" s="38"/>
-      <c r="C99" s="48" t="s">
+      <c r="C99" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D99" s="48"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
-      <c r="J99" s="48"/>
-      <c r="K99" s="48"/>
-      <c r="L99" s="48"/>
+      <c r="D99" s="46"/>
+      <c r="E99" s="46"/>
+      <c r="F99" s="46"/>
+      <c r="G99" s="46"/>
+      <c r="H99" s="46"/>
+      <c r="I99" s="46"/>
+      <c r="J99" s="46"/>
+      <c r="K99" s="46"/>
+      <c r="L99" s="46"/>
     </row>
     <row r="100" spans="1:12" ht="21.75" customHeight="1">
       <c r="A100" s="3"/>
@@ -14599,30 +14601,36 @@
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="C55:L55"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="A45:L50"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A52:L52"/>
-    <mergeCell ref="C53:L53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:L54"/>
-    <mergeCell ref="C65:L65"/>
-    <mergeCell ref="A56:L56"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="C58:L58"/>
-    <mergeCell ref="C59:L59"/>
-    <mergeCell ref="A60:L60"/>
-    <mergeCell ref="C61:L61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C62:L62"/>
-    <mergeCell ref="C63:L63"/>
-    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="A96:L96"/>
+    <mergeCell ref="C97:L97"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C99:L99"/>
+    <mergeCell ref="C95:L95"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:L86"/>
+    <mergeCell ref="C87:L87"/>
+    <mergeCell ref="A88:L88"/>
+    <mergeCell ref="C89:L89"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C91:L91"/>
+    <mergeCell ref="A92:L92"/>
+    <mergeCell ref="C93:L93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:L94"/>
+    <mergeCell ref="C85:L85"/>
+    <mergeCell ref="A76:L76"/>
+    <mergeCell ref="C77:L77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:L78"/>
+    <mergeCell ref="C79:L79"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="C81:L81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C83:L83"/>
+    <mergeCell ref="A84:L84"/>
     <mergeCell ref="C75:L75"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="C66:L66"/>
@@ -14636,36 +14644,30 @@
     <mergeCell ref="C73:L73"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C85:L85"/>
-    <mergeCell ref="A76:L76"/>
-    <mergeCell ref="C77:L77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:L78"/>
-    <mergeCell ref="C79:L79"/>
-    <mergeCell ref="A80:L80"/>
-    <mergeCell ref="C81:L81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C83:L83"/>
-    <mergeCell ref="A84:L84"/>
-    <mergeCell ref="C95:L95"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="C86:L86"/>
-    <mergeCell ref="C87:L87"/>
-    <mergeCell ref="A88:L88"/>
-    <mergeCell ref="C89:L89"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C91:L91"/>
-    <mergeCell ref="A92:L92"/>
-    <mergeCell ref="C93:L93"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:L94"/>
-    <mergeCell ref="A96:L96"/>
-    <mergeCell ref="C97:L97"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C99:L99"/>
+    <mergeCell ref="C65:L65"/>
+    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:L58"/>
+    <mergeCell ref="C59:L59"/>
+    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="C61:L61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:L62"/>
+    <mergeCell ref="C63:L63"/>
+    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="C55:L55"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A45:L50"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="C53:L53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:L54"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.18" top="0.42" bottom="0.18" header="0.24" footer="0.08"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200"/>

--- a/data/staging/source/1.2electric.xlsx
+++ b/data/staging/source/1.2electric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maejo365-my.sharepoint.com/personal/researchmju_mju_ac_th/Documents/RAE-Document-Center/07-GreenOffice/resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{B123507F-AE86-4D30-ACF2-EB8587520D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B49EF2D6-495F-4705-ABAC-DE2A7DDBD4B8}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{B123507F-AE86-4D30-ACF2-EB8587520D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5BB4550-4BE0-4937-A895-B99CFE5328BC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{150D84F5-2079-49F3-B53F-3CC6B2C0B5A9}"/>
   </bookViews>
@@ -764,6 +764,9 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -779,32 +782,29 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1120,7 +1120,7 @@
                   <c:v>43975.200000000186</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-8038867.2000000002</c:v>
+                  <c:v>37210.399999999441</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1135,7 +1135,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-647856.06666666665</c:v>
+                  <c:v>25150.399999999983</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2030,7 +2030,7 @@
                   <c:v>467.82127659574667</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-85519.863829787239</c:v>
+                  <c:v>395.85531914893022</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -2045,7 +2045,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-6892.0858156028371</c:v>
+                  <c:v>267.55744680851046</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2430,7 +2430,7 @@
                   <c:v>403036.79999999981</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-7774272.7999999998</c:v>
+                  <c:v>301804.79999999981</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2748,7 +2748,7 @@
                   <c:v>386.5594288368174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-82705.029787234045</c:v>
+                  <c:v>3210.689361702126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10825,41 +10825,41 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:16" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:16" s="6" customFormat="1" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42" t="s">
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="42"/>
+      <c r="K3" s="43"/>
       <c r="M3" s="7" t="s">
         <v>6</v>
       </c>
@@ -10868,7 +10868,7 @@
       <c r="P3" s="8"/>
     </row>
     <row r="4" spans="1:16" s="6" customFormat="1" ht="54" customHeight="1" thickBot="1">
-      <c r="A4" s="41"/>
+      <c r="A4" s="42"/>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -11334,34 +11334,36 @@
       </c>
       <c r="G12" s="13">
         <f t="shared" si="1"/>
-        <v>-8038867.2000000002</v>
+        <v>37210.399999999441</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="2"/>
-        <v>-43570660.223999999</v>
+        <v>201680.36799999696</v>
       </c>
       <c r="I12" s="12">
         <f t="shared" si="3"/>
-        <v>-85519.863829787239</v>
+        <v>395.85531914893022</v>
       </c>
       <c r="J12" s="14">
         <f t="shared" si="4"/>
-        <v>-205.23951219512196</v>
+        <v>-5.4613821138225577E-2</v>
       </c>
       <c r="K12" s="15">
         <f t="shared" si="5"/>
-        <v>-2988.5460560456672</v>
+        <v>12.828787190797232</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="18">
+        <v>8076077.5999999996</v>
+      </c>
       <c r="O12" s="18">
         <v>8038867.2000000002</v>
       </c>
       <c r="P12" s="18">
         <f t="shared" si="6"/>
-        <v>-8038867.2000000002</v>
+        <v>37210.399999999441</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="24.95" customHeight="1" thickBot="1">
@@ -11602,23 +11604,23 @@
       </c>
       <c r="G17" s="12">
         <f t="shared" si="7"/>
-        <v>-647856.06666666665</v>
+        <v>25150.399999999983</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="7"/>
-        <v>-3511379.881333333</v>
+        <v>136315.16799999992</v>
       </c>
       <c r="I17" s="12">
         <f>G17/F17</f>
-        <v>-6892.0858156028371</v>
+        <v>267.55744680851046</v>
       </c>
       <c r="J17" s="14">
         <f>(G17-C17)/C17</f>
-        <v>-20.289238104312069</v>
+        <v>-0.25117309387132908</v>
       </c>
       <c r="K17" s="15">
         <f>(I17-E17)/E17</f>
-        <v>-214.95165559949962</v>
+        <v>7.3058104968834927</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="24.95" customHeight="1">
@@ -11647,23 +11649,23 @@
       </c>
       <c r="G18" s="12">
         <f t="shared" si="8"/>
-        <v>-7774272.7999999998</v>
+        <v>301804.79999999981</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="8"/>
-        <v>-42136558.575999998</v>
+        <v>1635782.0159999989</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" si="8"/>
-        <v>-82705.029787234045</v>
+        <v>3210.689361702126</v>
       </c>
       <c r="J18" s="14">
         <f>(G18-C18)/C18</f>
-        <v>-20.289238104312073</v>
+        <v>-0.25117309387132897</v>
       </c>
       <c r="K18" s="15">
         <f t="shared" si="5"/>
-        <v>-214.95165559949965</v>
+        <v>7.3058104968834936</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="21.75" customHeight="1">
@@ -11707,90 +11709,90 @@
     </row>
     <row r="40" spans="1:12" ht="21.95" customHeight="1"/>
     <row r="43" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A43" s="43" t="s">
+      <c r="A43" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="43"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="43"/>
-      <c r="K43" s="43"/>
-      <c r="L43" s="43"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
     </row>
     <row r="44" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A44" s="43"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="43"/>
-      <c r="L44" s="43"/>
+      <c r="A44" s="44"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
+      <c r="L44" s="44"/>
     </row>
     <row r="45" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A45" s="43"/>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
+      <c r="A45" s="44"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="44"/>
     </row>
     <row r="46" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A46" s="43"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="J46" s="43"/>
-      <c r="K46" s="43"/>
-      <c r="L46" s="43"/>
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="44"/>
     </row>
     <row r="47" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A47" s="43"/>
-      <c r="B47" s="43"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="43"/>
-      <c r="I47" s="43"/>
-      <c r="J47" s="43"/>
-      <c r="K47" s="43"/>
-      <c r="L47" s="43"/>
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
     </row>
     <row r="48" spans="1:12" ht="21.6" customHeight="1">
-      <c r="A48" s="43"/>
-      <c r="B48" s="43"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="43"/>
-      <c r="J48" s="43"/>
-      <c r="K48" s="43"/>
-      <c r="L48" s="43"/>
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="44"/>
     </row>
     <row r="49" spans="1:12" ht="35.1" customHeight="1">
       <c r="A49" s="23"/>
@@ -11811,20 +11813,20 @@
       <c r="L49" s="23"/>
     </row>
     <row r="50" spans="1:12" ht="42" customHeight="1">
-      <c r="A50" s="44" t="s">
+      <c r="A50" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="44"/>
-      <c r="C50" s="44"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="44"/>
-      <c r="I50" s="44"/>
-      <c r="J50" s="44"/>
-      <c r="K50" s="44"/>
-      <c r="L50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
     </row>
     <row r="51" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
       <c r="A51" s="26" t="s">
@@ -11863,10 +11865,10 @@
       <c r="L52" s="30"/>
     </row>
     <row r="53" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A53" s="45" t="s">
+      <c r="A53" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B53" s="45"/>
+      <c r="B53" s="40"/>
       <c r="C53" s="31"/>
       <c r="D53" s="32"/>
       <c r="E53" s="30"/>
@@ -11931,10 +11933,10 @@
       <c r="L56" s="30"/>
     </row>
     <row r="57" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A57" s="45" t="s">
+      <c r="A57" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="45"/>
+      <c r="B57" s="40"/>
       <c r="C57" s="31"/>
       <c r="D57" s="32"/>
       <c r="E57" s="30"/>
@@ -12271,10 +12273,10 @@
       <c r="L76" s="30"/>
     </row>
     <row r="77" spans="1:12" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A77" s="45" t="s">
+      <c r="A77" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B77" s="45"/>
+      <c r="B77" s="40"/>
       <c r="C77" s="31"/>
       <c r="D77" s="32"/>
       <c r="E77" s="30"/>
@@ -12339,10 +12341,10 @@
       <c r="L80" s="30"/>
     </row>
     <row r="81" spans="1:19" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A81" s="45" t="s">
+      <c r="A81" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B81" s="45"/>
+      <c r="B81" s="40"/>
       <c r="C81" s="31"/>
       <c r="D81" s="32"/>
       <c r="E81" s="30"/>
@@ -12671,13 +12673,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A93:B93"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:A4"/>
@@ -12690,6 +12685,13 @@
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A93:B93"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.18" top="0.28999999999999998" bottom="0.18" header="0.24" footer="0.08"/>
   <pageSetup paperSize="9" scale="68" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId1"/>
@@ -12742,41 +12744,41 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:17" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:17" s="6" customFormat="1" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42" t="s">
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="42"/>
+      <c r="K3" s="43"/>
       <c r="N3" s="7" t="s">
         <v>6</v>
       </c>
@@ -12785,7 +12787,7 @@
       <c r="Q3" s="8"/>
     </row>
     <row r="4" spans="1:17" s="6" customFormat="1" ht="54" customHeight="1" thickBot="1">
-      <c r="A4" s="41"/>
+      <c r="A4" s="42"/>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -13628,700 +13630,700 @@
     </row>
     <row r="40" spans="1:12" ht="21.95" customHeight="1"/>
     <row r="45" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A45" s="47" t="s">
+      <c r="A45" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="47"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
-      <c r="L45" s="47"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
     </row>
     <row r="46" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A46" s="47"/>
-      <c r="B46" s="47"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
-      <c r="L46" s="47"/>
+      <c r="A46" s="52"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="52"/>
     </row>
     <row r="47" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A47" s="47"/>
-      <c r="B47" s="47"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="47"/>
-      <c r="I47" s="47"/>
-      <c r="J47" s="47"/>
-      <c r="K47" s="47"/>
-      <c r="L47" s="47"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="52"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="52"/>
     </row>
     <row r="48" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A48" s="47"/>
-      <c r="B48" s="47"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="47"/>
-      <c r="I48" s="47"/>
-      <c r="J48" s="47"/>
-      <c r="K48" s="47"/>
-      <c r="L48" s="47"/>
+      <c r="A48" s="52"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
+      <c r="K48" s="52"/>
+      <c r="L48" s="52"/>
     </row>
     <row r="49" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A49" s="47"/>
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="47"/>
-      <c r="K49" s="47"/>
-      <c r="L49" s="47"/>
+      <c r="A49" s="52"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="52"/>
+      <c r="K49" s="52"/>
+      <c r="L49" s="52"/>
     </row>
     <row r="50" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A50" s="47"/>
-      <c r="B50" s="47"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
-      <c r="I50" s="47"/>
-      <c r="J50" s="47"/>
-      <c r="K50" s="47"/>
-      <c r="L50" s="47"/>
+      <c r="A50" s="52"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="52"/>
+      <c r="K50" s="52"/>
+      <c r="L50" s="52"/>
     </row>
     <row r="51" spans="1:12" ht="42" customHeight="1">
-      <c r="A51" s="48" t="s">
+      <c r="A51" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="48"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
-      <c r="L51" s="48"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
     </row>
     <row r="52" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A52" s="49" t="s">
+      <c r="A52" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="B52" s="49"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
-      <c r="G52" s="49"/>
-      <c r="H52" s="49"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="49"/>
-      <c r="K52" s="49"/>
-      <c r="L52" s="49"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="46"/>
     </row>
     <row r="53" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A53" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B53" s="38"/>
-      <c r="C53" s="50" t="s">
+      <c r="C53" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="D53" s="50"/>
-      <c r="E53" s="50"/>
-      <c r="F53" s="50"/>
-      <c r="G53" s="50"/>
-      <c r="H53" s="50"/>
-      <c r="I53" s="50"/>
-      <c r="J53" s="50"/>
-      <c r="K53" s="50"/>
-      <c r="L53" s="50"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="47"/>
+      <c r="K53" s="47"/>
+      <c r="L53" s="47"/>
     </row>
     <row r="54" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A54" s="51" t="s">
+      <c r="A54" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="51"/>
-      <c r="C54" s="46" t="s">
+      <c r="B54" s="49"/>
+      <c r="C54" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
+      <c r="D54" s="48"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="48"/>
+      <c r="H54" s="48"/>
+      <c r="I54" s="48"/>
+      <c r="J54" s="48"/>
+      <c r="K54" s="48"/>
+      <c r="L54" s="48"/>
     </row>
     <row r="55" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A55" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B55" s="38"/>
-      <c r="C55" s="46" t="s">
+      <c r="C55" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="46"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="48"/>
+      <c r="L55" s="48"/>
     </row>
     <row r="56" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A56" s="49" t="s">
+      <c r="A56" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="B56" s="49"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="49"/>
-      <c r="J56" s="49"/>
-      <c r="K56" s="49"/>
-      <c r="L56" s="49"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="46"/>
+      <c r="I56" s="46"/>
+      <c r="J56" s="46"/>
+      <c r="K56" s="46"/>
+      <c r="L56" s="46"/>
     </row>
     <row r="57" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A57" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B57" s="38"/>
-      <c r="C57" s="50" t="s">
+      <c r="C57" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="D57" s="50"/>
-      <c r="E57" s="50"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="50"/>
-      <c r="I57" s="50"/>
-      <c r="J57" s="50"/>
-      <c r="K57" s="50"/>
-      <c r="L57" s="50"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="47"/>
+      <c r="K57" s="47"/>
+      <c r="L57" s="47"/>
     </row>
     <row r="58" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A58" s="51" t="s">
+      <c r="A58" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="B58" s="51"/>
-      <c r="C58" s="46" t="s">
+      <c r="B58" s="49"/>
+      <c r="C58" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="46"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48"/>
+      <c r="L58" s="48"/>
     </row>
     <row r="59" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A59" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B59" s="38"/>
-      <c r="C59" s="46" t="s">
+      <c r="C59" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="46"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
-      <c r="K59" s="46"/>
-      <c r="L59" s="46"/>
+      <c r="D59" s="48"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
+      <c r="L59" s="48"/>
     </row>
     <row r="60" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A60" s="49" t="s">
+      <c r="A60" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49"/>
-      <c r="F60" s="49"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="49"/>
-      <c r="I60" s="49"/>
-      <c r="J60" s="49"/>
-      <c r="K60" s="49"/>
-      <c r="L60" s="49"/>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="46"/>
+      <c r="I60" s="46"/>
+      <c r="J60" s="46"/>
+      <c r="K60" s="46"/>
+      <c r="L60" s="46"/>
     </row>
     <row r="61" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A61" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B61" s="38"/>
-      <c r="C61" s="50" t="s">
+      <c r="C61" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="D61" s="50"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="50"/>
-      <c r="G61" s="50"/>
-      <c r="H61" s="50"/>
-      <c r="I61" s="50"/>
-      <c r="J61" s="50"/>
-      <c r="K61" s="50"/>
-      <c r="L61" s="50"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47"/>
+      <c r="H61" s="47"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="47"/>
+      <c r="K61" s="47"/>
+      <c r="L61" s="47"/>
     </row>
     <row r="62" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A62" s="50" t="s">
+      <c r="A62" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B62" s="50"/>
-      <c r="C62" s="52" t="s">
+      <c r="B62" s="47"/>
+      <c r="C62" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="D62" s="52"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="52"/>
-      <c r="G62" s="52"/>
-      <c r="H62" s="52"/>
-      <c r="I62" s="52"/>
-      <c r="J62" s="52"/>
-      <c r="K62" s="52"/>
-      <c r="L62" s="52"/>
+      <c r="D62" s="51"/>
+      <c r="E62" s="51"/>
+      <c r="F62" s="51"/>
+      <c r="G62" s="51"/>
+      <c r="H62" s="51"/>
+      <c r="I62" s="51"/>
+      <c r="J62" s="51"/>
+      <c r="K62" s="51"/>
+      <c r="L62" s="51"/>
     </row>
     <row r="63" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A63" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B63" s="38"/>
-      <c r="C63" s="46" t="s">
+      <c r="C63" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46"/>
-      <c r="I63" s="46"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="46"/>
-      <c r="L63" s="46"/>
+      <c r="D63" s="48"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
+      <c r="L63" s="48"/>
     </row>
     <row r="64" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A64" s="49" t="s">
+      <c r="A64" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="49"/>
-      <c r="C64" s="49"/>
-      <c r="D64" s="49"/>
-      <c r="E64" s="49"/>
-      <c r="F64" s="49"/>
-      <c r="G64" s="49"/>
-      <c r="H64" s="49"/>
-      <c r="I64" s="49"/>
-      <c r="J64" s="49"/>
-      <c r="K64" s="49"/>
-      <c r="L64" s="49"/>
+      <c r="B64" s="46"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="46"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="46"/>
+      <c r="I64" s="46"/>
+      <c r="J64" s="46"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="46"/>
     </row>
     <row r="65" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A65" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B65" s="38"/>
-      <c r="C65" s="50" t="s">
+      <c r="C65" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="D65" s="50"/>
-      <c r="E65" s="50"/>
-      <c r="F65" s="50"/>
-      <c r="G65" s="50"/>
-      <c r="H65" s="50"/>
-      <c r="I65" s="50"/>
-      <c r="J65" s="50"/>
-      <c r="K65" s="50"/>
-      <c r="L65" s="50"/>
+      <c r="D65" s="47"/>
+      <c r="E65" s="47"/>
+      <c r="F65" s="47"/>
+      <c r="G65" s="47"/>
+      <c r="H65" s="47"/>
+      <c r="I65" s="47"/>
+      <c r="J65" s="47"/>
+      <c r="K65" s="47"/>
+      <c r="L65" s="47"/>
     </row>
     <row r="66" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A66" s="50" t="s">
+      <c r="A66" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B66" s="50"/>
-      <c r="C66" s="46" t="s">
+      <c r="B66" s="47"/>
+      <c r="C66" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="46"/>
-      <c r="K66" s="46"/>
-      <c r="L66" s="46"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
+      <c r="L66" s="48"/>
     </row>
     <row r="67" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A67" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B67" s="38"/>
-      <c r="C67" s="46" t="s">
+      <c r="C67" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="46"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="46"/>
-      <c r="L67" s="46"/>
+      <c r="D67" s="48"/>
+      <c r="E67" s="48"/>
+      <c r="F67" s="48"/>
+      <c r="G67" s="48"/>
+      <c r="H67" s="48"/>
+      <c r="I67" s="48"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
+      <c r="L67" s="48"/>
     </row>
     <row r="68" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A68" s="49" t="s">
+      <c r="A68" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B68" s="49"/>
-      <c r="C68" s="49"/>
-      <c r="D68" s="49"/>
-      <c r="E68" s="49"/>
-      <c r="F68" s="49"/>
-      <c r="G68" s="49"/>
-      <c r="H68" s="49"/>
-      <c r="I68" s="49"/>
-      <c r="J68" s="49"/>
-      <c r="K68" s="49"/>
-      <c r="L68" s="49"/>
+      <c r="B68" s="46"/>
+      <c r="C68" s="46"/>
+      <c r="D68" s="46"/>
+      <c r="E68" s="46"/>
+      <c r="F68" s="46"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="46"/>
+      <c r="I68" s="46"/>
+      <c r="J68" s="46"/>
+      <c r="K68" s="46"/>
+      <c r="L68" s="46"/>
     </row>
     <row r="69" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A69" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B69" s="38"/>
-      <c r="C69" s="50" t="s">
+      <c r="C69" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="D69" s="50"/>
-      <c r="E69" s="50"/>
-      <c r="F69" s="50"/>
-      <c r="G69" s="50"/>
-      <c r="H69" s="50"/>
-      <c r="I69" s="50"/>
-      <c r="J69" s="50"/>
-      <c r="K69" s="50"/>
-      <c r="L69" s="50"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
+      <c r="J69" s="47"/>
+      <c r="K69" s="47"/>
+      <c r="L69" s="47"/>
     </row>
     <row r="70" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A70" s="50" t="s">
+      <c r="A70" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B70" s="50"/>
-      <c r="C70" s="46" t="s">
+      <c r="B70" s="47"/>
+      <c r="C70" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
-      <c r="L70" s="46"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48"/>
+      <c r="L70" s="48"/>
     </row>
     <row r="71" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A71" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B71" s="38"/>
-      <c r="C71" s="46" t="s">
+      <c r="C71" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
-      <c r="L71" s="46"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48"/>
+      <c r="L71" s="48"/>
     </row>
     <row r="72" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A72" s="49" t="s">
+      <c r="A72" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="B72" s="49"/>
-      <c r="C72" s="49"/>
-      <c r="D72" s="49"/>
-      <c r="E72" s="49"/>
-      <c r="F72" s="49"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="49"/>
-      <c r="I72" s="49"/>
-      <c r="J72" s="49"/>
-      <c r="K72" s="49"/>
-      <c r="L72" s="49"/>
+      <c r="B72" s="46"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="46"/>
+      <c r="I72" s="46"/>
+      <c r="J72" s="46"/>
+      <c r="K72" s="46"/>
+      <c r="L72" s="46"/>
     </row>
     <row r="73" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A73" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B73" s="38"/>
-      <c r="C73" s="50" t="s">
+      <c r="C73" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="D73" s="50"/>
-      <c r="E73" s="50"/>
-      <c r="F73" s="50"/>
-      <c r="G73" s="50"/>
-      <c r="H73" s="50"/>
-      <c r="I73" s="50"/>
-      <c r="J73" s="50"/>
-      <c r="K73" s="50"/>
-      <c r="L73" s="50"/>
+      <c r="D73" s="47"/>
+      <c r="E73" s="47"/>
+      <c r="F73" s="47"/>
+      <c r="G73" s="47"/>
+      <c r="H73" s="47"/>
+      <c r="I73" s="47"/>
+      <c r="J73" s="47"/>
+      <c r="K73" s="47"/>
+      <c r="L73" s="47"/>
     </row>
     <row r="74" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A74" s="50" t="s">
+      <c r="A74" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B74" s="50"/>
-      <c r="C74" s="53" t="s">
+      <c r="B74" s="47"/>
+      <c r="C74" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="D74" s="53"/>
-      <c r="E74" s="53"/>
-      <c r="F74" s="53"/>
-      <c r="G74" s="53"/>
-      <c r="H74" s="53"/>
-      <c r="I74" s="53"/>
-      <c r="J74" s="53"/>
-      <c r="K74" s="53"/>
-      <c r="L74" s="53"/>
+      <c r="D74" s="50"/>
+      <c r="E74" s="50"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
+      <c r="H74" s="50"/>
+      <c r="I74" s="50"/>
+      <c r="J74" s="50"/>
+      <c r="K74" s="50"/>
+      <c r="L74" s="50"/>
     </row>
     <row r="75" spans="1:12" s="27" customFormat="1" ht="50.1" customHeight="1">
       <c r="A75" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B75" s="38"/>
-      <c r="C75" s="46" t="s">
+      <c r="C75" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-      <c r="L75" s="46"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
+      <c r="L75" s="48"/>
     </row>
     <row r="76" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A76" s="49" t="s">
+      <c r="A76" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
-      <c r="J76" s="49"/>
-      <c r="K76" s="49"/>
-      <c r="L76" s="49"/>
+      <c r="B76" s="46"/>
+      <c r="C76" s="46"/>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="46"/>
+      <c r="I76" s="46"/>
+      <c r="J76" s="46"/>
+      <c r="K76" s="46"/>
+      <c r="L76" s="46"/>
     </row>
     <row r="77" spans="1:12" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A77" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B77" s="38"/>
-      <c r="C77" s="50" t="s">
+      <c r="C77" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="50"/>
-      <c r="E77" s="50"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="50"/>
-      <c r="H77" s="50"/>
-      <c r="I77" s="50"/>
-      <c r="J77" s="50"/>
-      <c r="K77" s="50"/>
-      <c r="L77" s="50"/>
+      <c r="D77" s="47"/>
+      <c r="E77" s="47"/>
+      <c r="F77" s="47"/>
+      <c r="G77" s="47"/>
+      <c r="H77" s="47"/>
+      <c r="I77" s="47"/>
+      <c r="J77" s="47"/>
+      <c r="K77" s="47"/>
+      <c r="L77" s="47"/>
     </row>
     <row r="78" spans="1:12" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A78" s="51" t="s">
+      <c r="A78" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="B78" s="51"/>
-      <c r="C78" s="46" t="s">
+      <c r="B78" s="49"/>
+      <c r="C78" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="D78" s="46"/>
-      <c r="E78" s="46"/>
-      <c r="F78" s="46"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="46"/>
-      <c r="I78" s="46"/>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
-      <c r="L78" s="46"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="48"/>
+      <c r="K78" s="48"/>
+      <c r="L78" s="48"/>
     </row>
     <row r="79" spans="1:12" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A79" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B79" s="38"/>
-      <c r="C79" s="46" t="s">
+      <c r="C79" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="D79" s="46"/>
-      <c r="E79" s="46"/>
-      <c r="F79" s="46"/>
-      <c r="G79" s="46"/>
-      <c r="H79" s="46"/>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-      <c r="L79" s="46"/>
+      <c r="D79" s="48"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
+      <c r="I79" s="48"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="48"/>
+      <c r="L79" s="48"/>
     </row>
     <row r="80" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A80" s="49" t="s">
+      <c r="A80" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
-      <c r="J80" s="49"/>
-      <c r="K80" s="49"/>
-      <c r="L80" s="49"/>
+      <c r="B80" s="46"/>
+      <c r="C80" s="46"/>
+      <c r="D80" s="46"/>
+      <c r="E80" s="46"/>
+      <c r="F80" s="46"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="46"/>
+      <c r="I80" s="46"/>
+      <c r="J80" s="46"/>
+      <c r="K80" s="46"/>
+      <c r="L80" s="46"/>
     </row>
     <row r="81" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A81" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B81" s="38"/>
-      <c r="C81" s="50" t="s">
+      <c r="C81" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="50"/>
-      <c r="I81" s="50"/>
-      <c r="J81" s="50"/>
-      <c r="K81" s="50"/>
-      <c r="L81" s="50"/>
+      <c r="D81" s="47"/>
+      <c r="E81" s="47"/>
+      <c r="F81" s="47"/>
+      <c r="G81" s="47"/>
+      <c r="H81" s="47"/>
+      <c r="I81" s="47"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="47"/>
+      <c r="L81" s="47"/>
     </row>
     <row r="82" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A82" s="51" t="s">
+      <c r="A82" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="B82" s="51"/>
-      <c r="C82" s="46" t="s">
+      <c r="B82" s="49"/>
+      <c r="C82" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="D82" s="46"/>
-      <c r="E82" s="46"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="46"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="46"/>
-      <c r="L82" s="46"/>
+      <c r="D82" s="48"/>
+      <c r="E82" s="48"/>
+      <c r="F82" s="48"/>
+      <c r="G82" s="48"/>
+      <c r="H82" s="48"/>
+      <c r="I82" s="48"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="48"/>
+      <c r="L82" s="48"/>
     </row>
     <row r="83" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A83" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B83" s="38"/>
-      <c r="C83" s="46" t="s">
+      <c r="C83" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D83" s="46"/>
-      <c r="E83" s="46"/>
-      <c r="F83" s="46"/>
-      <c r="G83" s="46"/>
-      <c r="H83" s="46"/>
-      <c r="I83" s="46"/>
-      <c r="J83" s="46"/>
-      <c r="K83" s="46"/>
-      <c r="L83" s="46"/>
+      <c r="D83" s="48"/>
+      <c r="E83" s="48"/>
+      <c r="F83" s="48"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="48"/>
+      <c r="I83" s="48"/>
+      <c r="J83" s="48"/>
+      <c r="K83" s="48"/>
+      <c r="L83" s="48"/>
     </row>
     <row r="84" spans="1:20" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A84" s="49" t="s">
+      <c r="A84" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="B84" s="49"/>
-      <c r="C84" s="49"/>
-      <c r="D84" s="49"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="49"/>
-      <c r="G84" s="49"/>
-      <c r="H84" s="49"/>
-      <c r="I84" s="49"/>
-      <c r="J84" s="49"/>
-      <c r="K84" s="49"/>
-      <c r="L84" s="49"/>
+      <c r="B84" s="46"/>
+      <c r="C84" s="46"/>
+      <c r="D84" s="46"/>
+      <c r="E84" s="46"/>
+      <c r="F84" s="46"/>
+      <c r="G84" s="46"/>
+      <c r="H84" s="46"/>
+      <c r="I84" s="46"/>
+      <c r="J84" s="46"/>
+      <c r="K84" s="46"/>
+      <c r="L84" s="46"/>
     </row>
     <row r="85" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A85" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B85" s="38"/>
-      <c r="C85" s="50" t="s">
+      <c r="C85" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="D85" s="50"/>
-      <c r="E85" s="50"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="50"/>
-      <c r="H85" s="50"/>
-      <c r="I85" s="50"/>
-      <c r="J85" s="50"/>
-      <c r="K85" s="50"/>
-      <c r="L85" s="50"/>
+      <c r="D85" s="47"/>
+      <c r="E85" s="47"/>
+      <c r="F85" s="47"/>
+      <c r="G85" s="47"/>
+      <c r="H85" s="47"/>
+      <c r="I85" s="47"/>
+      <c r="J85" s="47"/>
+      <c r="K85" s="47"/>
+      <c r="L85" s="47"/>
       <c r="M85" s="34"/>
       <c r="N85" s="34"/>
       <c r="O85" s="34"/>
@@ -14332,22 +14334,22 @@
       <c r="T85" s="34"/>
     </row>
     <row r="86" spans="1:20" s="27" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A86" s="50" t="s">
+      <c r="A86" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B86" s="50"/>
-      <c r="C86" s="46" t="s">
+      <c r="B86" s="47"/>
+      <c r="C86" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="D86" s="46"/>
-      <c r="E86" s="46"/>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="46"/>
-      <c r="I86" s="46"/>
-      <c r="J86" s="46"/>
-      <c r="K86" s="46"/>
-      <c r="L86" s="46"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
+      <c r="J86" s="48"/>
+      <c r="K86" s="48"/>
+      <c r="L86" s="48"/>
       <c r="M86" s="34"/>
       <c r="N86" s="34"/>
       <c r="O86" s="34"/>
@@ -14362,18 +14364,18 @@
         <v>51</v>
       </c>
       <c r="B87" s="38"/>
-      <c r="C87" s="46" t="s">
+      <c r="C87" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D87" s="46"/>
-      <c r="E87" s="46"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="46"/>
-      <c r="I87" s="46"/>
-      <c r="J87" s="46"/>
-      <c r="K87" s="46"/>
-      <c r="L87" s="46"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
+      <c r="L87" s="48"/>
       <c r="M87" s="34"/>
       <c r="N87" s="34"/>
       <c r="O87" s="34"/>
@@ -14384,214 +14386,214 @@
       <c r="T87" s="34"/>
     </row>
     <row r="88" spans="1:20" s="27" customFormat="1" ht="30" customHeight="1">
-      <c r="A88" s="49" t="s">
+      <c r="A88" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49"/>
-      <c r="J88" s="49"/>
-      <c r="K88" s="49"/>
-      <c r="L88" s="49"/>
+      <c r="B88" s="46"/>
+      <c r="C88" s="46"/>
+      <c r="D88" s="46"/>
+      <c r="E88" s="46"/>
+      <c r="F88" s="46"/>
+      <c r="G88" s="46"/>
+      <c r="H88" s="46"/>
+      <c r="I88" s="46"/>
+      <c r="J88" s="46"/>
+      <c r="K88" s="46"/>
+      <c r="L88" s="46"/>
     </row>
     <row r="89" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A89" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B89" s="38"/>
-      <c r="C89" s="50" t="s">
+      <c r="C89" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="D89" s="50"/>
-      <c r="E89" s="50"/>
-      <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
-      <c r="H89" s="50"/>
-      <c r="I89" s="50"/>
-      <c r="J89" s="50"/>
-      <c r="K89" s="50"/>
-      <c r="L89" s="50"/>
+      <c r="D89" s="47"/>
+      <c r="E89" s="47"/>
+      <c r="F89" s="47"/>
+      <c r="G89" s="47"/>
+      <c r="H89" s="47"/>
+      <c r="I89" s="47"/>
+      <c r="J89" s="47"/>
+      <c r="K89" s="47"/>
+      <c r="L89" s="47"/>
     </row>
     <row r="90" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A90" s="50" t="s">
+      <c r="A90" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B90" s="50"/>
-      <c r="C90" s="46" t="s">
+      <c r="B90" s="47"/>
+      <c r="C90" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="D90" s="46"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="46"/>
-      <c r="K90" s="46"/>
-      <c r="L90" s="46"/>
+      <c r="D90" s="48"/>
+      <c r="E90" s="48"/>
+      <c r="F90" s="48"/>
+      <c r="G90" s="48"/>
+      <c r="H90" s="48"/>
+      <c r="I90" s="48"/>
+      <c r="J90" s="48"/>
+      <c r="K90" s="48"/>
+      <c r="L90" s="48"/>
     </row>
     <row r="91" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A91" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B91" s="38"/>
-      <c r="C91" s="46" t="s">
+      <c r="C91" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D91" s="46"/>
-      <c r="E91" s="46"/>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46"/>
-      <c r="I91" s="46"/>
-      <c r="J91" s="46"/>
-      <c r="K91" s="46"/>
-      <c r="L91" s="46"/>
+      <c r="D91" s="48"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="48"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="48"/>
+      <c r="I91" s="48"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="48"/>
+      <c r="L91" s="48"/>
     </row>
     <row r="92" spans="1:20" s="35" customFormat="1" ht="30" customHeight="1">
-      <c r="A92" s="49" t="s">
+      <c r="A92" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="B92" s="49"/>
-      <c r="C92" s="49"/>
-      <c r="D92" s="49"/>
-      <c r="E92" s="49"/>
-      <c r="F92" s="49"/>
-      <c r="G92" s="49"/>
-      <c r="H92" s="49"/>
-      <c r="I92" s="49"/>
-      <c r="J92" s="49"/>
-      <c r="K92" s="49"/>
-      <c r="L92" s="49"/>
+      <c r="B92" s="46"/>
+      <c r="C92" s="46"/>
+      <c r="D92" s="46"/>
+      <c r="E92" s="46"/>
+      <c r="F92" s="46"/>
+      <c r="G92" s="46"/>
+      <c r="H92" s="46"/>
+      <c r="I92" s="46"/>
+      <c r="J92" s="46"/>
+      <c r="K92" s="46"/>
+      <c r="L92" s="46"/>
     </row>
     <row r="93" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A93" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B93" s="38"/>
-      <c r="C93" s="50" t="s">
+      <c r="C93" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="D93" s="50"/>
-      <c r="E93" s="50"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="50"/>
-      <c r="H93" s="50"/>
-      <c r="I93" s="50"/>
-      <c r="J93" s="50"/>
-      <c r="K93" s="50"/>
-      <c r="L93" s="50"/>
+      <c r="D93" s="47"/>
+      <c r="E93" s="47"/>
+      <c r="F93" s="47"/>
+      <c r="G93" s="47"/>
+      <c r="H93" s="47"/>
+      <c r="I93" s="47"/>
+      <c r="J93" s="47"/>
+      <c r="K93" s="47"/>
+      <c r="L93" s="47"/>
     </row>
     <row r="94" spans="1:20" s="35" customFormat="1" ht="81" customHeight="1">
-      <c r="A94" s="50" t="s">
+      <c r="A94" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B94" s="50"/>
-      <c r="C94" s="46" t="s">
+      <c r="B94" s="47"/>
+      <c r="C94" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="D94" s="46"/>
-      <c r="E94" s="46"/>
-      <c r="F94" s="46"/>
-      <c r="G94" s="46"/>
-      <c r="H94" s="46"/>
-      <c r="I94" s="46"/>
-      <c r="J94" s="46"/>
-      <c r="K94" s="46"/>
-      <c r="L94" s="46"/>
+      <c r="D94" s="48"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+      <c r="H94" s="48"/>
+      <c r="I94" s="48"/>
+      <c r="J94" s="48"/>
+      <c r="K94" s="48"/>
+      <c r="L94" s="48"/>
     </row>
     <row r="95" spans="1:20" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A95" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B95" s="38"/>
-      <c r="C95" s="46" t="s">
+      <c r="C95" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D95" s="46"/>
-      <c r="E95" s="46"/>
-      <c r="F95" s="46"/>
-      <c r="G95" s="46"/>
-      <c r="H95" s="46"/>
-      <c r="I95" s="46"/>
-      <c r="J95" s="46"/>
-      <c r="K95" s="46"/>
-      <c r="L95" s="46"/>
+      <c r="D95" s="48"/>
+      <c r="E95" s="48"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="48"/>
+      <c r="H95" s="48"/>
+      <c r="I95" s="48"/>
+      <c r="J95" s="48"/>
+      <c r="K95" s="48"/>
+      <c r="L95" s="48"/>
     </row>
     <row r="96" spans="1:20" s="35" customFormat="1" ht="30" customHeight="1">
-      <c r="A96" s="49" t="s">
+      <c r="A96" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="B96" s="49"/>
-      <c r="C96" s="49"/>
-      <c r="D96" s="49"/>
-      <c r="E96" s="49"/>
-      <c r="F96" s="49"/>
-      <c r="G96" s="49"/>
-      <c r="H96" s="49"/>
-      <c r="I96" s="49"/>
-      <c r="J96" s="49"/>
-      <c r="K96" s="49"/>
-      <c r="L96" s="49"/>
+      <c r="B96" s="46"/>
+      <c r="C96" s="46"/>
+      <c r="D96" s="46"/>
+      <c r="E96" s="46"/>
+      <c r="F96" s="46"/>
+      <c r="G96" s="46"/>
+      <c r="H96" s="46"/>
+      <c r="I96" s="46"/>
+      <c r="J96" s="46"/>
+      <c r="K96" s="46"/>
+      <c r="L96" s="46"/>
     </row>
     <row r="97" spans="1:12" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A97" s="38" t="s">
         <v>49</v>
       </c>
       <c r="B97" s="38"/>
-      <c r="C97" s="50" t="s">
+      <c r="C97" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="D97" s="50"/>
-      <c r="E97" s="50"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="50"/>
-      <c r="H97" s="50"/>
-      <c r="I97" s="50"/>
-      <c r="J97" s="50"/>
-      <c r="K97" s="50"/>
-      <c r="L97" s="50"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="47"/>
+      <c r="G97" s="47"/>
+      <c r="H97" s="47"/>
+      <c r="I97" s="47"/>
+      <c r="J97" s="47"/>
+      <c r="K97" s="47"/>
+      <c r="L97" s="47"/>
     </row>
     <row r="98" spans="1:12" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A98" s="50" t="s">
+      <c r="A98" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B98" s="50"/>
-      <c r="C98" s="46" t="s">
+      <c r="B98" s="47"/>
+      <c r="C98" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="D98" s="46"/>
-      <c r="E98" s="46"/>
-      <c r="F98" s="46"/>
-      <c r="G98" s="46"/>
-      <c r="H98" s="46"/>
-      <c r="I98" s="46"/>
-      <c r="J98" s="46"/>
-      <c r="K98" s="46"/>
-      <c r="L98" s="46"/>
+      <c r="D98" s="48"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="48"/>
+      <c r="L98" s="48"/>
     </row>
     <row r="99" spans="1:12" s="35" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A99" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B99" s="38"/>
-      <c r="C99" s="46" t="s">
+      <c r="C99" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D99" s="46"/>
-      <c r="E99" s="46"/>
-      <c r="F99" s="46"/>
-      <c r="G99" s="46"/>
-      <c r="H99" s="46"/>
-      <c r="I99" s="46"/>
-      <c r="J99" s="46"/>
-      <c r="K99" s="46"/>
-      <c r="L99" s="46"/>
+      <c r="D99" s="48"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="48"/>
+      <c r="L99" s="48"/>
     </row>
     <row r="100" spans="1:12" ht="21.75" customHeight="1">
       <c r="A100" s="3"/>
@@ -14601,11 +14603,55 @@
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="A96:L96"/>
-    <mergeCell ref="C97:L97"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C99:L99"/>
+    <mergeCell ref="C55:L55"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A45:L50"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="C53:L53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:L54"/>
+    <mergeCell ref="C65:L65"/>
+    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:L58"/>
+    <mergeCell ref="C59:L59"/>
+    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="C61:L61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:L62"/>
+    <mergeCell ref="C63:L63"/>
+    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="C75:L75"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C67:L67"/>
+    <mergeCell ref="A68:L68"/>
+    <mergeCell ref="C69:L69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:L70"/>
+    <mergeCell ref="C71:L71"/>
+    <mergeCell ref="A72:L72"/>
+    <mergeCell ref="C73:L73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C85:L85"/>
+    <mergeCell ref="A76:L76"/>
+    <mergeCell ref="C77:L77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:L78"/>
+    <mergeCell ref="C79:L79"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="C81:L81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C83:L83"/>
+    <mergeCell ref="A84:L84"/>
     <mergeCell ref="C95:L95"/>
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="C86:L86"/>
@@ -14619,55 +14665,11 @@
     <mergeCell ref="C93:L93"/>
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="C94:L94"/>
-    <mergeCell ref="C85:L85"/>
-    <mergeCell ref="A76:L76"/>
-    <mergeCell ref="C77:L77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:L78"/>
-    <mergeCell ref="C79:L79"/>
-    <mergeCell ref="A80:L80"/>
-    <mergeCell ref="C81:L81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C83:L83"/>
-    <mergeCell ref="A84:L84"/>
-    <mergeCell ref="C75:L75"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="C67:L67"/>
-    <mergeCell ref="A68:L68"/>
-    <mergeCell ref="C69:L69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:L70"/>
-    <mergeCell ref="C71:L71"/>
-    <mergeCell ref="A72:L72"/>
-    <mergeCell ref="C73:L73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C65:L65"/>
-    <mergeCell ref="A56:L56"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="C58:L58"/>
-    <mergeCell ref="C59:L59"/>
-    <mergeCell ref="A60:L60"/>
-    <mergeCell ref="C61:L61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C62:L62"/>
-    <mergeCell ref="C63:L63"/>
-    <mergeCell ref="A64:L64"/>
-    <mergeCell ref="C55:L55"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="A45:L50"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A52:L52"/>
-    <mergeCell ref="C53:L53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:L54"/>
+    <mergeCell ref="A96:L96"/>
+    <mergeCell ref="C97:L97"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C99:L99"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.18" top="0.42" bottom="0.18" header="0.24" footer="0.08"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200"/>
